--- a/data/macro/USA/FED Target Rate.xlsx
+++ b/data/macro/USA/FED Target Rate.xlsx
@@ -1,25 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/USA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6122CD0-78E2-42E6-976B-CF920622E4D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BAB65B-25D5-1043-B009-5D946A430E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10155" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10160" yWindow="780" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fed Target Rate" sheetId="1" r:id="rId1"/>
     <sheet name="info" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -63,27 +74,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -91,14 +102,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -107,7 +118,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -138,22 +149,30 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -432,40 +451,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G295"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" style="7" customWidth="1"/>
     <col min="5" max="7" width="9" style="3"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>30221</v>
       </c>
@@ -473,13 +492,32 @@
         <v>30221</v>
       </c>
       <c r="C2" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D2" s="7" t="str">
+        <f>IF(
+ AND(
+  B2 &gt;= IF(
+         YEAR(B2)&gt;=2007,
+         DATE(YEAR(B2),3,14)-WEEKDAY(DATE(YEAR(B2),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B2),4,7)-WEEKDAY(DATE(YEAR(B2),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B2 &lt;  IF(
+         YEAR(B2)&gt;=2007,
+         DATE(YEAR(B2),11,7)-WEEKDAY(DATE(YEAR(B2),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B2),10,31)-WEEKDAY(DATE(YEAR(B2),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
       <c r="E2" s="3">
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>30225</v>
       </c>
@@ -487,7 +525,26 @@
         <v>30225</v>
       </c>
       <c r="C3" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D3" s="7" t="str">
+        <f t="shared" ref="D3:D66" si="0">IF(
+ AND(
+  B3 &gt;= IF(
+         YEAR(B3)&gt;=2007,
+         DATE(YEAR(B3),3,14)-WEEKDAY(DATE(YEAR(B3),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B3),4,7)-WEEKDAY(DATE(YEAR(B3),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B3 &lt;  IF(
+         YEAR(B3)&gt;=2007,
+         DATE(YEAR(B3),11,7)-WEEKDAY(DATE(YEAR(B3),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B3),10,31)-WEEKDAY(DATE(YEAR(B3),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
       <c r="E3" s="3">
         <v>0.1</v>
@@ -496,7 +553,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>30231</v>
       </c>
@@ -504,7 +561,11 @@
         <v>30231</v>
       </c>
       <c r="C4" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D4" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E4" s="3">
         <v>9.5000000000000001E-2</v>
@@ -513,7 +574,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>30274</v>
       </c>
@@ -521,7 +582,11 @@
         <v>30274</v>
       </c>
       <c r="C5" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D5" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E5" s="3">
         <v>0.09</v>
@@ -530,7 +595,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>30299</v>
       </c>
@@ -538,7 +603,11 @@
         <v>30299</v>
       </c>
       <c r="C6" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D6" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E6" s="3">
         <v>8.5000000000000006E-2</v>
@@ -547,7 +616,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>30406</v>
       </c>
@@ -555,7 +624,11 @@
         <v>30406</v>
       </c>
       <c r="C7" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D7" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E7" s="3">
         <v>8.6199999999999999E-2</v>
@@ -564,7 +637,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>30461</v>
       </c>
@@ -572,7 +645,11 @@
         <v>30461</v>
       </c>
       <c r="C8" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D8" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E8" s="3">
         <v>8.7499999999999994E-2</v>
@@ -581,7 +658,7 @@
         <v>8.6199999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>30491</v>
       </c>
@@ -589,7 +666,11 @@
         <v>30491</v>
       </c>
       <c r="C9" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D9" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E9" s="3">
         <v>0.09</v>
@@ -598,7 +679,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>30511</v>
       </c>
@@ -606,7 +687,11 @@
         <v>30511</v>
       </c>
       <c r="C10" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D10" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E10" s="3">
         <v>9.2499999999999999E-2</v>
@@ -615,7 +700,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>30517</v>
       </c>
@@ -623,7 +708,11 @@
         <v>30517</v>
       </c>
       <c r="C11" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D11" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E11" s="3">
         <v>9.4299999999999995E-2</v>
@@ -632,7 +721,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>30539</v>
       </c>
@@ -640,7 +729,11 @@
         <v>30539</v>
       </c>
       <c r="C12" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D12" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E12" s="3">
         <v>9.5600000000000004E-2</v>
@@ -649,7 +742,7 @@
         <v>9.4299999999999995E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>30545</v>
       </c>
@@ -657,7 +750,11 @@
         <v>30545</v>
       </c>
       <c r="C13" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D13" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E13" s="3">
         <v>9.5000000000000001E-2</v>
@@ -666,7 +763,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>30574</v>
       </c>
@@ -674,7 +771,11 @@
         <v>30574</v>
       </c>
       <c r="C14" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D14" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E14" s="3">
         <v>9.3700000000000006E-2</v>
@@ -683,7 +784,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>30770</v>
       </c>
@@ -691,7 +792,11 @@
         <v>30770</v>
       </c>
       <c r="C15" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D15" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E15" s="3">
         <v>0.105</v>
@@ -700,7 +805,7 @@
         <v>9.3700000000000006E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>30868</v>
       </c>
@@ -708,7 +813,11 @@
         <v>30868</v>
       </c>
       <c r="C16" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D16" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E16" s="3">
         <v>0.11</v>
@@ -717,7 +826,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>30882</v>
       </c>
@@ -725,7 +834,11 @@
         <v>30882</v>
       </c>
       <c r="C17" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D17" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E17" s="3">
         <v>0.1125</v>
@@ -734,7 +847,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>30903</v>
       </c>
@@ -742,7 +855,11 @@
         <v>30903</v>
       </c>
       <c r="C18" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D18" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E18" s="3">
         <v>0.115</v>
@@ -751,7 +868,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>30945</v>
       </c>
@@ -759,7 +876,11 @@
         <v>30945</v>
       </c>
       <c r="C19" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D19" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E19" s="3">
         <v>0.1125</v>
@@ -768,7 +889,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>30952</v>
       </c>
@@ -776,7 +897,11 @@
         <v>30952</v>
       </c>
       <c r="C20" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D20" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E20" s="3">
         <v>0.11</v>
@@ -785,7 +910,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>30966</v>
       </c>
@@ -793,7 +918,11 @@
         <v>30966</v>
       </c>
       <c r="C21" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D21" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E21" s="3">
         <v>0.105</v>
@@ -802,7 +931,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>30973</v>
       </c>
@@ -810,7 +939,11 @@
         <v>30973</v>
       </c>
       <c r="C22" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D22" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E22" s="3">
         <v>0.1</v>
@@ -819,7 +952,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>30994</v>
       </c>
@@ -827,7 +960,11 @@
         <v>30994</v>
       </c>
       <c r="C23" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D23" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E23" s="3">
         <v>9.5000000000000001E-2</v>
@@ -836,7 +973,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>31009</v>
       </c>
@@ -844,7 +981,11 @@
         <v>31009</v>
       </c>
       <c r="C24" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D24" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E24" s="3">
         <v>0.09</v>
@@ -853,7 +994,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>31022</v>
       </c>
@@ -861,7 +1002,11 @@
         <v>31022</v>
       </c>
       <c r="C25" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D25" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E25" s="3">
         <v>8.7499999999999994E-2</v>
@@ -870,7 +1015,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>31035</v>
       </c>
@@ -878,7 +1023,11 @@
         <v>31035</v>
       </c>
       <c r="C26" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D26" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E26" s="3">
         <v>8.5000000000000006E-2</v>
@@ -887,7 +1036,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>31040</v>
       </c>
@@ -895,7 +1044,11 @@
         <v>31040</v>
       </c>
       <c r="C27" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D27" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E27" s="3">
         <v>8.1199999999999994E-2</v>
@@ -904,7 +1057,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>31071</v>
       </c>
@@ -912,7 +1065,11 @@
         <v>31071</v>
       </c>
       <c r="C28" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D28" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E28" s="3">
         <v>8.2500000000000004E-2</v>
@@ -921,7 +1078,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>31092</v>
       </c>
@@ -929,7 +1086,11 @@
         <v>31092</v>
       </c>
       <c r="C29" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D29" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E29" s="3">
         <v>8.3699999999999997E-2</v>
@@ -938,7 +1099,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>31134</v>
       </c>
@@ -946,7 +1107,11 @@
         <v>31134</v>
       </c>
       <c r="C30" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D30" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E30" s="3">
         <v>8.5000000000000006E-2</v>
@@ -955,7 +1120,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>31162</v>
       </c>
@@ -963,7 +1128,11 @@
         <v>31162</v>
       </c>
       <c r="C31" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D31" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E31" s="3">
         <v>8.2500000000000004E-2</v>
@@ -972,7 +1141,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31187</v>
       </c>
@@ -980,7 +1149,11 @@
         <v>31187</v>
       </c>
       <c r="C32" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D32" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E32" s="3">
         <v>7.7499999999999999E-2</v>
@@ -989,7 +1162,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31239</v>
       </c>
@@ -997,7 +1170,11 @@
         <v>31239</v>
       </c>
       <c r="C33" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D33" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E33" s="3">
         <v>7.6799999999999993E-2</v>
@@ -1006,7 +1183,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>31253</v>
       </c>
@@ -1014,7 +1191,11 @@
         <v>31253</v>
       </c>
       <c r="C34" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D34" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E34" s="3">
         <v>7.7499999999999999E-2</v>
@@ -1023,7 +1204,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>31280</v>
       </c>
@@ -1031,7 +1212,11 @@
         <v>31280</v>
       </c>
       <c r="C35" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D35" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E35" s="3">
         <v>7.8100000000000003E-2</v>
@@ -1040,7 +1225,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>31296</v>
       </c>
@@ -1048,7 +1233,11 @@
         <v>31296</v>
       </c>
       <c r="C36" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D36" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E36" s="3">
         <v>0.08</v>
@@ -1057,7 +1246,7 @@
         <v>7.8100000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>31399</v>
       </c>
@@ -1065,7 +1254,11 @@
         <v>31399</v>
       </c>
       <c r="C37" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D37" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E37" s="3">
         <v>7.7499999999999999E-2</v>
@@ -1074,7 +1267,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>31478</v>
       </c>
@@ -1082,7 +1275,11 @@
         <v>31478</v>
       </c>
       <c r="C38" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D38" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E38" s="3">
         <v>7.2499999999999995E-2</v>
@@ -1091,7 +1288,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>31504</v>
       </c>
@@ -1099,7 +1296,11 @@
         <v>31504</v>
       </c>
       <c r="C39" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D39" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E39" s="3">
         <v>7.3099999999999998E-2</v>
@@ -1108,7 +1309,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>31523</v>
       </c>
@@ -1116,7 +1317,11 @@
         <v>31523</v>
       </c>
       <c r="C40" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D40" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E40" s="3">
         <v>6.7500000000000004E-2</v>
@@ -1125,7 +1330,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>31554</v>
       </c>
@@ -1133,7 +1338,11 @@
         <v>31554</v>
       </c>
       <c r="C41" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D41" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E41" s="3">
         <v>6.8099999999999994E-2</v>
@@ -1142,7 +1351,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>31568</v>
       </c>
@@ -1150,7 +1359,11 @@
         <v>31568</v>
       </c>
       <c r="C42" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D42" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E42" s="3">
         <v>6.8699999999999997E-2</v>
@@ -1159,7 +1372,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>31604</v>
       </c>
@@ -1167,7 +1380,11 @@
         <v>31604</v>
       </c>
       <c r="C43" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D43" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E43" s="3">
         <v>6.3700000000000007E-2</v>
@@ -1176,7 +1393,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>31645</v>
       </c>
@@ -1184,7 +1401,11 @@
         <v>31645</v>
       </c>
       <c r="C44" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D44" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E44" s="3">
         <v>5.8700000000000002E-2</v>
@@ -1193,7 +1414,7 @@
         <v>6.3700000000000007E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>31782</v>
       </c>
@@ -1201,7 +1422,11 @@
         <v>31782</v>
       </c>
       <c r="C45" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D45" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E45" s="3">
         <v>0.06</v>
@@ -1210,7 +1435,7 @@
         <v>5.8700000000000002E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>31897</v>
       </c>
@@ -1218,7 +1443,11 @@
         <v>31897</v>
       </c>
       <c r="C46" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D46" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E46" s="3">
         <v>6.5000000000000002E-2</v>
@@ -1227,7 +1456,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>31919</v>
       </c>
@@ -1235,7 +1464,11 @@
         <v>31919</v>
       </c>
       <c r="C47" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D47" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E47" s="3">
         <v>6.7500000000000004E-2</v>
@@ -1244,7 +1477,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>31960</v>
       </c>
@@ -1252,7 +1485,11 @@
         <v>31960</v>
       </c>
       <c r="C48" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D48" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E48" s="3">
         <v>6.6199999999999995E-2</v>
@@ -1261,7 +1498,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>32016</v>
       </c>
@@ -1269,7 +1506,11 @@
         <v>32016</v>
       </c>
       <c r="C49" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D49" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E49" s="3">
         <v>6.7500000000000004E-2</v>
@@ -1278,7 +1519,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>32023</v>
       </c>
@@ -1286,7 +1527,11 @@
         <v>32023</v>
       </c>
       <c r="C50" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D50" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E50" s="3">
         <v>6.8699999999999997E-2</v>
@@ -1295,7 +1540,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>32024</v>
       </c>
@@ -1303,7 +1548,11 @@
         <v>32024</v>
       </c>
       <c r="C51" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D51" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E51" s="3">
         <v>7.2499999999999995E-2</v>
@@ -1312,7 +1561,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>32044</v>
       </c>
@@ -1320,7 +1569,11 @@
         <v>32044</v>
       </c>
       <c r="C52" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D52" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E52" s="3">
         <v>7.3099999999999998E-2</v>
@@ -1329,7 +1582,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>32085</v>
       </c>
@@ -1337,7 +1590,11 @@
         <v>32085</v>
       </c>
       <c r="C53" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D53" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E53" s="3">
         <v>6.8099999999999994E-2</v>
@@ -1346,7 +1603,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>32170</v>
       </c>
@@ -1354,7 +1611,11 @@
         <v>32170</v>
       </c>
       <c r="C54" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D54" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E54" s="3">
         <v>6.6199999999999995E-2</v>
@@ -1363,7 +1624,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>32184</v>
       </c>
@@ -1371,7 +1632,11 @@
         <v>32184</v>
       </c>
       <c r="C55" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D55" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E55" s="3">
         <v>6.5000000000000002E-2</v>
@@ -1380,7 +1645,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>32232</v>
       </c>
@@ -1388,7 +1653,11 @@
         <v>32232</v>
       </c>
       <c r="C56" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D56" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E56" s="3">
         <v>6.7500000000000004E-2</v>
@@ -1397,7 +1666,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>32272</v>
       </c>
@@ -1405,7 +1674,11 @@
         <v>32272</v>
       </c>
       <c r="C57" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D57" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E57" s="3">
         <v>7.0000000000000007E-2</v>
@@ -1414,7 +1687,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>32288</v>
       </c>
@@ -1422,7 +1695,11 @@
         <v>32288</v>
       </c>
       <c r="C58" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D58" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E58" s="3">
         <v>7.2499999999999995E-2</v>
@@ -1431,7 +1708,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>32316</v>
       </c>
@@ -1439,7 +1716,11 @@
         <v>32316</v>
       </c>
       <c r="C59" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D59" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E59" s="3">
         <v>7.4300000000000005E-2</v>
@@ -1448,7 +1729,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>32325</v>
       </c>
@@ -1456,7 +1737,11 @@
         <v>32325</v>
       </c>
       <c r="C60" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D60" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E60" s="3">
         <v>7.4999999999999997E-2</v>
@@ -1465,7 +1750,7 @@
         <v>7.4300000000000005E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>32343</v>
       </c>
@@ -1473,7 +1758,11 @@
         <v>32343</v>
       </c>
       <c r="C61" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D61" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E61" s="3">
         <v>7.6799999999999993E-2</v>
@@ -1482,7 +1771,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>32363</v>
       </c>
@@ -1490,7 +1779,11 @@
         <v>32363</v>
       </c>
       <c r="C62" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D62" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E62" s="3">
         <v>7.7499999999999999E-2</v>
@@ -1499,7 +1792,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>32364</v>
       </c>
@@ -1507,7 +1800,11 @@
         <v>32364</v>
       </c>
       <c r="C63" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D63" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-4</v>
       </c>
       <c r="E63" s="3">
         <v>8.1199999999999994E-2</v>
@@ -1516,7 +1813,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>32464</v>
       </c>
@@ -1524,7 +1821,11 @@
         <v>32464</v>
       </c>
       <c r="C64" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D64" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E64" s="3">
         <v>8.3099999999999993E-2</v>
@@ -1533,7 +1834,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>32469</v>
       </c>
@@ -1541,7 +1842,11 @@
         <v>32469</v>
       </c>
       <c r="C65" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D65" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E65" s="3">
         <v>8.3699999999999997E-2</v>
@@ -1550,7 +1855,7 @@
         <v>8.3099999999999993E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>32492</v>
       </c>
@@ -1558,7 +1863,11 @@
         <v>32492</v>
       </c>
       <c r="C66" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D66" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v>UTC-5</v>
       </c>
       <c r="E66" s="3">
         <v>8.6800000000000002E-2</v>
@@ -1567,7 +1876,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>32513</v>
       </c>
@@ -1575,7 +1884,26 @@
         <v>32513</v>
       </c>
       <c r="C67" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D67" s="7" t="str">
+        <f t="shared" ref="D67:D130" si="1">IF(
+ AND(
+  B67 &gt;= IF(
+         YEAR(B67)&gt;=2007,
+         DATE(YEAR(B67),3,14)-WEEKDAY(DATE(YEAR(B67),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B67),4,7)-WEEKDAY(DATE(YEAR(B67),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B67 &lt;  IF(
+         YEAR(B67)&gt;=2007,
+         DATE(YEAR(B67),11,7)-WEEKDAY(DATE(YEAR(B67),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B67),10,31)-WEEKDAY(DATE(YEAR(B67),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-5</v>
       </c>
       <c r="E67" s="3">
         <v>0.09</v>
@@ -1584,7 +1912,7 @@
         <v>8.6800000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>32548</v>
       </c>
@@ -1592,7 +1920,11 @@
         <v>32548</v>
       </c>
       <c r="C68" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D68" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E68" s="3">
         <v>9.1200000000000003E-2</v>
@@ -1601,7 +1933,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>32553</v>
       </c>
@@ -1609,7 +1941,11 @@
         <v>32553</v>
       </c>
       <c r="C69" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D69" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E69" s="3">
         <v>9.3100000000000002E-2</v>
@@ -1618,7 +1954,7 @@
         <v>9.1200000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>32563</v>
       </c>
@@ -1626,7 +1962,11 @@
         <v>32563</v>
       </c>
       <c r="C70" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D70" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E70" s="3">
         <v>9.7500000000000003E-2</v>
@@ -1635,7 +1975,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>32645</v>
       </c>
@@ -1643,7 +1983,11 @@
         <v>32645</v>
       </c>
       <c r="C71" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D71" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E71" s="3">
         <v>9.8100000000000007E-2</v>
@@ -1652,7 +1996,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>32665</v>
       </c>
@@ -1660,7 +2004,11 @@
         <v>32665</v>
       </c>
       <c r="C72" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D72" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E72" s="3">
         <v>9.5600000000000004E-2</v>
@@ -1669,7 +2017,7 @@
         <v>9.8100000000000007E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>32696</v>
       </c>
@@ -1677,7 +2025,11 @@
         <v>32696</v>
       </c>
       <c r="C73" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D73" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E73" s="3">
         <v>9.3100000000000002E-2</v>
@@ -1686,7 +2038,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>32716</v>
       </c>
@@ -1694,7 +2046,11 @@
         <v>32716</v>
       </c>
       <c r="C74" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D74" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E74" s="3">
         <v>9.06E-2</v>
@@ -1703,7 +2059,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>32800</v>
       </c>
@@ -1711,7 +2067,11 @@
         <v>32800</v>
       </c>
       <c r="C75" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D75" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E75" s="3">
         <v>8.7499999999999994E-2</v>
@@ -1720,7 +2080,7 @@
         <v>9.06E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>32818</v>
       </c>
@@ -1728,7 +2088,11 @@
         <v>32818</v>
       </c>
       <c r="C76" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D76" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E76" s="3">
         <v>8.5000000000000006E-2</v>
@@ -1737,7 +2101,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>32862</v>
       </c>
@@ -1745,7 +2109,11 @@
         <v>32862</v>
       </c>
       <c r="C77" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D77" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E77" s="3">
         <v>8.2500000000000004E-2</v>
@@ -1754,7 +2122,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>33067</v>
       </c>
@@ -1762,7 +2130,11 @@
         <v>33067</v>
       </c>
       <c r="C78" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D78" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E78" s="3">
         <v>0.08</v>
@@ -1771,7 +2143,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>33175</v>
       </c>
@@ -1779,7 +2151,11 @@
         <v>33175</v>
       </c>
       <c r="C79" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D79" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E79" s="3">
         <v>7.7499999999999999E-2</v>
@@ -1788,7 +2164,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>33191</v>
       </c>
@@ -1796,7 +2172,11 @@
         <v>33191</v>
       </c>
       <c r="C80" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D80" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E80" s="3">
         <v>7.4999999999999997E-2</v>
@@ -1805,7 +2185,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>33214</v>
       </c>
@@ -1813,7 +2193,11 @@
         <v>33214</v>
       </c>
       <c r="C81" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D81" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E81" s="3">
         <v>7.2499999999999995E-2</v>
@@ -1822,7 +2206,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>33226</v>
       </c>
@@ -1830,7 +2214,11 @@
         <v>33226</v>
       </c>
       <c r="C82" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D82" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E82" s="3">
         <v>7.0000000000000007E-2</v>
@@ -1839,7 +2227,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>33247</v>
       </c>
@@ -1847,7 +2235,11 @@
         <v>33247</v>
       </c>
       <c r="C83" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D83" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E83" s="3">
         <v>6.7500000000000004E-2</v>
@@ -1856,7 +2248,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>33270</v>
       </c>
@@ -1864,7 +2256,11 @@
         <v>33270</v>
       </c>
       <c r="C84" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D84" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E84" s="3">
         <v>6.25E-2</v>
@@ -1873,7 +2269,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>33305</v>
       </c>
@@ -1881,7 +2277,11 @@
         <v>33305</v>
       </c>
       <c r="C85" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D85" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E85" s="3">
         <v>0.06</v>
@@ -1890,7 +2290,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>33358</v>
       </c>
@@ -1898,7 +2298,11 @@
         <v>33358</v>
       </c>
       <c r="C86" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D86" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E86" s="3">
         <v>5.7500000000000002E-2</v>
@@ -1907,7 +2311,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>33456</v>
       </c>
@@ -1915,7 +2319,11 @@
         <v>33456</v>
       </c>
       <c r="C87" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D87" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E87" s="3">
         <v>5.5E-2</v>
@@ -1924,7 +2332,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>33494</v>
       </c>
@@ -1932,7 +2340,11 @@
         <v>33494</v>
       </c>
       <c r="C88" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D88" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E88" s="3">
         <v>5.2499999999999998E-2</v>
@@ -1941,7 +2353,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>33542</v>
       </c>
@@ -1949,7 +2361,11 @@
         <v>33542</v>
       </c>
       <c r="C89" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D89" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E89" s="3">
         <v>0.05</v>
@@ -1958,7 +2374,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>33548</v>
       </c>
@@ -1966,7 +2382,11 @@
         <v>33548</v>
       </c>
       <c r="C90" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D90" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E90" s="3">
         <v>4.7500000000000001E-2</v>
@@ -1975,7 +2395,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>33578</v>
       </c>
@@ -1983,7 +2403,11 @@
         <v>33578</v>
       </c>
       <c r="C91" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D91" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E91" s="3">
         <v>4.4999999999999998E-2</v>
@@ -1992,7 +2416,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>33592</v>
       </c>
@@ -2000,7 +2424,11 @@
         <v>33592</v>
       </c>
       <c r="C92" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D92" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E92" s="3">
         <v>0.04</v>
@@ -2009,7 +2437,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>33703</v>
       </c>
@@ -2017,7 +2445,11 @@
         <v>33703</v>
       </c>
       <c r="C93" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D93" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E93" s="3">
         <v>3.7499999999999999E-2</v>
@@ -2026,7 +2458,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>33787</v>
       </c>
@@ -2034,7 +2466,11 @@
         <v>33787</v>
       </c>
       <c r="C94" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D94" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E94" s="3">
         <v>3.2500000000000001E-2</v>
@@ -2043,7 +2479,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>33851</v>
       </c>
@@ -2051,7 +2487,11 @@
         <v>33851</v>
       </c>
       <c r="C95" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D95" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E95" s="3">
         <v>0.03</v>
@@ -2060,7 +2500,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>34369</v>
       </c>
@@ -2068,7 +2508,11 @@
         <v>34369</v>
       </c>
       <c r="C96" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D96" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E96" s="3">
         <v>3.2500000000000001E-2</v>
@@ -2077,7 +2521,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>34415</v>
       </c>
@@ -2085,7 +2529,11 @@
         <v>34415</v>
       </c>
       <c r="C97" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D97" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E97" s="3">
         <v>3.5000000000000003E-2</v>
@@ -2094,7 +2542,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>34442</v>
       </c>
@@ -2102,7 +2550,11 @@
         <v>34442</v>
       </c>
       <c r="C98" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D98" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E98" s="3">
         <v>3.7499999999999999E-2</v>
@@ -2111,7 +2563,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>34471</v>
       </c>
@@ -2119,7 +2571,11 @@
         <v>34471</v>
       </c>
       <c r="C99" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D99" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E99" s="3">
         <v>4.2500000000000003E-2</v>
@@ -2128,7 +2584,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>34562</v>
       </c>
@@ -2136,7 +2592,11 @@
         <v>34562</v>
       </c>
       <c r="C100" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D100" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E100" s="3">
         <v>4.7500000000000001E-2</v>
@@ -2145,7 +2605,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>34653</v>
       </c>
@@ -2153,7 +2613,11 @@
         <v>34653</v>
       </c>
       <c r="C101" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D101" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E101" s="3">
         <v>5.5E-2</v>
@@ -2162,7 +2626,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>34731</v>
       </c>
@@ -2170,7 +2634,11 @@
         <v>34731</v>
       </c>
       <c r="C102" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D102" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E102" s="3">
         <v>0.06</v>
@@ -2179,7 +2647,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>34886</v>
       </c>
@@ -2187,7 +2655,11 @@
         <v>34886</v>
       </c>
       <c r="C103" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D103" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E103" s="3">
         <v>5.7500000000000002E-2</v>
@@ -2196,7 +2668,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>35052</v>
       </c>
@@ -2204,7 +2676,11 @@
         <v>35052</v>
       </c>
       <c r="C104" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D104" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E104" s="3">
         <v>5.5E-2</v>
@@ -2213,7 +2689,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>35095</v>
       </c>
@@ -2221,7 +2697,11 @@
         <v>35095</v>
       </c>
       <c r="C105" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D105" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E105" s="3">
         <v>5.2499999999999998E-2</v>
@@ -2230,7 +2710,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>35514</v>
       </c>
@@ -2238,7 +2718,11 @@
         <v>35514</v>
       </c>
       <c r="C106" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D106" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E106" s="3">
         <v>5.5E-2</v>
@@ -2247,7 +2731,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>36067</v>
       </c>
@@ -2255,7 +2739,11 @@
         <v>36067</v>
       </c>
       <c r="C107" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D107" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E107" s="3">
         <v>5.2499999999999998E-2</v>
@@ -2264,7 +2752,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>36083</v>
       </c>
@@ -2272,7 +2760,11 @@
         <v>36083</v>
       </c>
       <c r="C108" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D108" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E108" s="3">
         <v>0.05</v>
@@ -2281,7 +2773,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>36116</v>
       </c>
@@ -2289,7 +2781,11 @@
         <v>36116</v>
       </c>
       <c r="C109" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D109" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E109" s="3">
         <v>4.7500000000000001E-2</v>
@@ -2298,7 +2794,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>36341</v>
       </c>
@@ -2306,7 +2802,11 @@
         <v>36341</v>
       </c>
       <c r="C110" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D110" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E110" s="3">
         <v>0.05</v>
@@ -2315,7 +2815,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>36396</v>
       </c>
@@ -2323,7 +2823,11 @@
         <v>36396</v>
       </c>
       <c r="C111" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D111" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E111" s="3">
         <v>5.2499999999999998E-2</v>
@@ -2332,7 +2836,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>36480</v>
       </c>
@@ -2340,7 +2844,11 @@
         <v>36480</v>
       </c>
       <c r="C112" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D112" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E112" s="3">
         <v>5.5E-2</v>
@@ -2349,7 +2857,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>36558</v>
       </c>
@@ -2357,7 +2865,11 @@
         <v>36558</v>
       </c>
       <c r="C113" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D113" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E113" s="3">
         <v>5.7500000000000002E-2</v>
@@ -2366,7 +2878,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>36606</v>
       </c>
@@ -2374,7 +2886,11 @@
         <v>36606</v>
       </c>
       <c r="C114" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D114" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E114" s="3">
         <v>0.06</v>
@@ -2383,7 +2899,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>36662</v>
       </c>
@@ -2391,7 +2907,11 @@
         <v>36662</v>
       </c>
       <c r="C115" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D115" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E115" s="3">
         <v>6.5000000000000002E-2</v>
@@ -2400,7 +2920,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>36894</v>
       </c>
@@ -2408,7 +2928,11 @@
         <v>36894</v>
       </c>
       <c r="C116" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D116" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E116" s="3">
         <v>0.06</v>
@@ -2417,7 +2941,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>36922</v>
       </c>
@@ -2425,7 +2949,11 @@
         <v>36922</v>
       </c>
       <c r="C117" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D117" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E117" s="3">
         <v>5.5E-2</v>
@@ -2434,7 +2962,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>36970</v>
       </c>
@@ -2442,7 +2970,11 @@
         <v>36970</v>
       </c>
       <c r="C118" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D118" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E118" s="3">
         <v>0.05</v>
@@ -2451,7 +2983,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>36999</v>
       </c>
@@ -2459,7 +2991,11 @@
         <v>36999</v>
       </c>
       <c r="C119" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D119" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E119" s="3">
         <v>4.4999999999999998E-2</v>
@@ -2468,7 +3004,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>37026</v>
       </c>
@@ -2476,7 +3012,11 @@
         <v>37026</v>
       </c>
       <c r="C120" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D120" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E120" s="3">
         <v>0.04</v>
@@ -2485,7 +3025,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>37069</v>
       </c>
@@ -2493,7 +3033,11 @@
         <v>37069</v>
       </c>
       <c r="C121" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D121" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E121" s="3">
         <v>3.7499999999999999E-2</v>
@@ -2502,7 +3046,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>37124</v>
       </c>
@@ -2510,7 +3054,11 @@
         <v>37124</v>
       </c>
       <c r="C122" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D122" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E122" s="3">
         <v>3.5000000000000003E-2</v>
@@ -2519,7 +3067,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>37151</v>
       </c>
@@ -2527,7 +3075,11 @@
         <v>37151</v>
       </c>
       <c r="C123" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D123" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E123" s="3">
         <v>0.03</v>
@@ -2536,7 +3088,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>37166</v>
       </c>
@@ -2544,7 +3096,11 @@
         <v>37166</v>
       </c>
       <c r="C124" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D124" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E124" s="3">
         <v>2.5000000000000001E-2</v>
@@ -2553,7 +3109,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>37201</v>
       </c>
@@ -2561,7 +3117,11 @@
         <v>37201</v>
       </c>
       <c r="C125" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D125" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E125" s="3">
         <v>0.02</v>
@@ -2570,7 +3130,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>37236</v>
       </c>
@@ -2578,7 +3138,11 @@
         <v>37236</v>
       </c>
       <c r="C126" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D126" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E126" s="3">
         <v>1.7500000000000002E-2</v>
@@ -2587,7 +3151,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>37566</v>
       </c>
@@ -2595,7 +3159,11 @@
         <v>37566</v>
       </c>
       <c r="C127" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D127" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-5</v>
       </c>
       <c r="E127" s="3">
         <v>1.2500000000000001E-2</v>
@@ -2604,7 +3172,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>37797</v>
       </c>
@@ -2612,7 +3180,11 @@
         <v>37797</v>
       </c>
       <c r="C128" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D128" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E128" s="3">
         <v>0.01</v>
@@ -2621,7 +3193,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>38168</v>
       </c>
@@ -2629,7 +3201,11 @@
         <v>38168</v>
       </c>
       <c r="C129" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D129" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E129" s="3">
         <v>1.2500000000000001E-2</v>
@@ -2638,7 +3214,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>38209</v>
       </c>
@@ -2646,7 +3222,11 @@
         <v>38209</v>
       </c>
       <c r="C130" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D130" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>UTC-4</v>
       </c>
       <c r="E130" s="3">
         <v>1.4999999999999999E-2</v>
@@ -2655,7 +3235,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>38251</v>
       </c>
@@ -2663,7 +3243,26 @@
         <v>38251</v>
       </c>
       <c r="C131" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D131" s="7" t="str">
+        <f t="shared" ref="D131:D194" si="2">IF(
+ AND(
+  B131 &gt;= IF(
+         YEAR(B131)&gt;=2007,
+         DATE(YEAR(B131),3,14)-WEEKDAY(DATE(YEAR(B131),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B131),4,7)-WEEKDAY(DATE(YEAR(B131),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B131 &lt;  IF(
+         YEAR(B131)&gt;=2007,
+         DATE(YEAR(B131),11,7)-WEEKDAY(DATE(YEAR(B131),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B131),10,31)-WEEKDAY(DATE(YEAR(B131),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
       <c r="E131" s="3">
         <v>1.7500000000000002E-2</v>
@@ -2672,7 +3271,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>38301</v>
       </c>
@@ -2680,7 +3279,11 @@
         <v>38301</v>
       </c>
       <c r="C132" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D132" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E132" s="3">
         <v>0.02</v>
@@ -2689,7 +3292,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>38335</v>
       </c>
@@ -2697,7 +3300,11 @@
         <v>38335</v>
       </c>
       <c r="C133" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D133" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E133" s="3">
         <v>2.2499999999999999E-2</v>
@@ -2706,7 +3313,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>38385</v>
       </c>
@@ -2714,7 +3321,11 @@
         <v>38385</v>
       </c>
       <c r="C134" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D134" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E134" s="3">
         <v>2.5000000000000001E-2</v>
@@ -2723,7 +3334,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>38433</v>
       </c>
@@ -2731,7 +3342,11 @@
         <v>38433</v>
       </c>
       <c r="C135" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D135" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E135" s="3">
         <v>2.75E-2</v>
@@ -2740,7 +3355,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>38475</v>
       </c>
@@ -2748,7 +3363,11 @@
         <v>38475</v>
       </c>
       <c r="C136" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D136" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E136" s="3">
         <v>0.03</v>
@@ -2757,7 +3376,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>38533</v>
       </c>
@@ -2765,7 +3384,11 @@
         <v>38533</v>
       </c>
       <c r="C137" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D137" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E137" s="3">
         <v>3.2500000000000001E-2</v>
@@ -2774,7 +3397,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>38573</v>
       </c>
@@ -2782,7 +3405,11 @@
         <v>38573</v>
       </c>
       <c r="C138" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D138" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E138" s="3">
         <v>3.5000000000000003E-2</v>
@@ -2791,7 +3418,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>38615</v>
       </c>
@@ -2799,7 +3426,11 @@
         <v>38615</v>
       </c>
       <c r="C139" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D139" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E139" s="3">
         <v>3.7499999999999999E-2</v>
@@ -2808,7 +3439,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>38657</v>
       </c>
@@ -2816,7 +3447,11 @@
         <v>38657</v>
       </c>
       <c r="C140" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D140" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E140" s="3">
         <v>0.04</v>
@@ -2825,7 +3460,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>38699</v>
       </c>
@@ -2833,7 +3468,11 @@
         <v>38699</v>
       </c>
       <c r="C141" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D141" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E141" s="3">
         <v>4.2500000000000003E-2</v>
@@ -2842,7 +3481,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>38748</v>
       </c>
@@ -2850,7 +3489,11 @@
         <v>38748</v>
       </c>
       <c r="C142" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D142" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E142" s="3">
         <v>4.4999999999999998E-2</v>
@@ -2859,7 +3502,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>38804</v>
       </c>
@@ -2867,7 +3510,11 @@
         <v>38804</v>
       </c>
       <c r="C143" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D143" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E143" s="3">
         <v>4.7500000000000001E-2</v>
@@ -2876,7 +3523,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>38847</v>
       </c>
@@ -2884,7 +3531,11 @@
         <v>38847</v>
       </c>
       <c r="C144" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D144" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E144" s="3">
         <v>0.05</v>
@@ -2893,7 +3544,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>38897</v>
       </c>
@@ -2901,7 +3552,11 @@
         <v>38897</v>
       </c>
       <c r="C145" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D145" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E145" s="3">
         <v>5.2499999999999998E-2</v>
@@ -2910,7 +3565,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>39343</v>
       </c>
@@ -2918,7 +3573,11 @@
         <v>39343</v>
       </c>
       <c r="C146" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D146" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E146" s="3">
         <v>4.7500000000000001E-2</v>
@@ -2927,7 +3586,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>39386</v>
       </c>
@@ -2935,7 +3594,11 @@
         <v>39386</v>
       </c>
       <c r="C147" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D147" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E147" s="3">
         <v>4.4999999999999998E-2</v>
@@ -2944,7 +3607,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>39427</v>
       </c>
@@ -2952,7 +3615,11 @@
         <v>39427</v>
       </c>
       <c r="C148" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D148" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E148" s="3">
         <v>4.2500000000000003E-2</v>
@@ -2961,7 +3628,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>39469</v>
       </c>
@@ -2969,7 +3636,11 @@
         <v>39469</v>
       </c>
       <c r="C149" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D149" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E149" s="3">
         <v>3.5000000000000003E-2</v>
@@ -2978,7 +3649,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>39477</v>
       </c>
@@ -2986,7 +3657,11 @@
         <v>39477</v>
       </c>
       <c r="C150" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D150" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
       </c>
       <c r="E150" s="3">
         <v>0.03</v>
@@ -2995,7 +3670,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>39525</v>
       </c>
@@ -3003,7 +3678,11 @@
         <v>39525</v>
       </c>
       <c r="C151" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D151" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E151" s="3">
         <v>2.2499999999999999E-2</v>
@@ -3015,7 +3694,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>39568</v>
       </c>
@@ -3023,7 +3702,11 @@
         <v>39568</v>
       </c>
       <c r="C152" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D152" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E152" s="3">
         <v>0.02</v>
@@ -3035,7 +3718,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>39624</v>
       </c>
@@ -3043,7 +3726,11 @@
         <v>39624</v>
       </c>
       <c r="C153" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D153" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E153" s="3">
         <v>0.02</v>
@@ -3055,7 +3742,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>39665</v>
       </c>
@@ -3063,7 +3750,11 @@
         <v>39665</v>
       </c>
       <c r="C154" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D154" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E154" s="3">
         <v>0.02</v>
@@ -3072,7 +3763,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>39707</v>
       </c>
@@ -3080,7 +3771,11 @@
         <v>39707</v>
       </c>
       <c r="C155" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D155" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E155" s="3">
         <v>0.02</v>
@@ -3092,7 +3787,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>39729</v>
       </c>
@@ -3100,7 +3795,11 @@
         <v>39729</v>
       </c>
       <c r="C156" s="2">
-        <v>0.25</v>
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="D156" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E156" s="3">
         <v>1.4999999999999999E-2</v>
@@ -3109,7 +3808,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>39750</v>
       </c>
@@ -3117,7 +3816,11 @@
         <v>39750</v>
       </c>
       <c r="C157" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D157" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E157" s="3">
         <v>0.01</v>
@@ -3129,7 +3832,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>39798</v>
       </c>
@@ -3139,6 +3842,10 @@
       <c r="C158" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D158" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E158" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3149,7 +3856,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>39841</v>
       </c>
@@ -3159,6 +3866,10 @@
       <c r="C159" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D159" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E159" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3169,7 +3880,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>39890</v>
       </c>
@@ -3177,7 +3888,11 @@
         <v>39890</v>
       </c>
       <c r="C160" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D160" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E160" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3189,7 +3904,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>39932</v>
       </c>
@@ -3197,7 +3912,11 @@
         <v>39932</v>
       </c>
       <c r="C161" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D161" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E161" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3209,7 +3928,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>39988</v>
       </c>
@@ -3217,7 +3936,11 @@
         <v>39988</v>
       </c>
       <c r="C162" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D162" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E162" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3229,7 +3952,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>40037</v>
       </c>
@@ -3237,7 +3960,11 @@
         <v>40037</v>
       </c>
       <c r="C163" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D163" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E163" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3249,7 +3976,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>40079</v>
       </c>
@@ -3257,7 +3984,11 @@
         <v>40079</v>
       </c>
       <c r="C164" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D164" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E164" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3269,7 +4000,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>40121</v>
       </c>
@@ -3279,6 +4010,10 @@
       <c r="C165" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D165" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E165" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3289,7 +4024,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>40163</v>
       </c>
@@ -3299,6 +4034,10 @@
       <c r="C166" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D166" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E166" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3309,7 +4048,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>40205</v>
       </c>
@@ -3319,6 +4058,10 @@
       <c r="C167" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D167" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E167" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3329,7 +4072,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>40253</v>
       </c>
@@ -3337,7 +4080,11 @@
         <v>40253</v>
       </c>
       <c r="C168" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D168" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E168" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3349,7 +4096,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>40296</v>
       </c>
@@ -3357,7 +4104,11 @@
         <v>40296</v>
       </c>
       <c r="C169" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D169" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E169" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3369,7 +4120,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>40352</v>
       </c>
@@ -3377,7 +4128,11 @@
         <v>40352</v>
       </c>
       <c r="C170" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D170" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E170" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3389,7 +4144,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>40400</v>
       </c>
@@ -3397,7 +4152,11 @@
         <v>40400</v>
       </c>
       <c r="C171" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D171" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E171" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3409,7 +4168,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>40442</v>
       </c>
@@ -3417,7 +4176,11 @@
         <v>40442</v>
       </c>
       <c r="C172" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D172" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E172" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3429,7 +4192,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>40485</v>
       </c>
@@ -3437,7 +4200,11 @@
         <v>40485</v>
       </c>
       <c r="C173" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D173" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E173" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3449,7 +4216,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>40526</v>
       </c>
@@ -3459,6 +4226,10 @@
       <c r="C174" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D174" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E174" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3469,7 +4240,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>40569</v>
       </c>
@@ -3479,6 +4250,10 @@
       <c r="C175" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D175" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E175" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3489,7 +4264,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>40617</v>
       </c>
@@ -3497,7 +4272,11 @@
         <v>40617</v>
       </c>
       <c r="C176" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D176" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E176" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3509,7 +4288,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>40660</v>
       </c>
@@ -3517,7 +4296,11 @@
         <v>40660</v>
       </c>
       <c r="C177" s="2">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D177" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E177" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3529,7 +4312,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>40716</v>
       </c>
@@ -3537,7 +4320,11 @@
         <v>40716</v>
       </c>
       <c r="C178" s="2">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D178" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E178" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3549,7 +4336,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>40764</v>
       </c>
@@ -3557,7 +4344,11 @@
         <v>40764</v>
       </c>
       <c r="C179" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D179" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E179" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3569,7 +4360,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>40807</v>
       </c>
@@ -3577,7 +4368,11 @@
         <v>40807</v>
       </c>
       <c r="C180" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D180" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E180" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3589,7 +4384,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>40849</v>
       </c>
@@ -3597,7 +4392,11 @@
         <v>40849</v>
       </c>
       <c r="C181" s="2">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D181" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E181" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3609,7 +4408,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>40890</v>
       </c>
@@ -3619,6 +4418,10 @@
       <c r="C182" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D182" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E182" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3629,7 +4432,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>40933</v>
       </c>
@@ -3639,6 +4442,10 @@
       <c r="C183" s="2">
         <v>0.52083333333333337</v>
       </c>
+      <c r="D183" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E183" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3649,7 +4456,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>40981</v>
       </c>
@@ -3657,7 +4464,11 @@
         <v>40981</v>
       </c>
       <c r="C184" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D184" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E184" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3669,7 +4480,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>41024</v>
       </c>
@@ -3677,7 +4488,11 @@
         <v>41024</v>
       </c>
       <c r="C185" s="2">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D185" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E185" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3689,7 +4504,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>41080</v>
       </c>
@@ -3697,7 +4512,11 @@
         <v>41080</v>
       </c>
       <c r="C186" s="2">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D186" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E186" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3709,7 +4528,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>41122</v>
       </c>
@@ -3717,7 +4536,11 @@
         <v>41122</v>
       </c>
       <c r="C187" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D187" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E187" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3729,7 +4552,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>41165</v>
       </c>
@@ -3737,7 +4560,11 @@
         <v>41165</v>
       </c>
       <c r="C188" s="2">
-        <v>0.47916666666666669</v>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="D188" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E188" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3749,7 +4576,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>41206</v>
       </c>
@@ -3757,7 +4584,11 @@
         <v>41206</v>
       </c>
       <c r="C189" s="2">
-        <v>0.55208333333333337</v>
+        <v>0.59375</v>
+      </c>
+      <c r="D189" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E189" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3769,7 +4600,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>41255</v>
       </c>
@@ -3779,6 +4610,10 @@
       <c r="C190" s="2">
         <v>0.52083333333333337</v>
       </c>
+      <c r="D190" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E190" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3789,7 +4624,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>41304</v>
       </c>
@@ -3799,6 +4634,10 @@
       <c r="C191" s="2">
         <v>0.59375</v>
       </c>
+      <c r="D191" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E191" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3809,7 +4648,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>41353</v>
       </c>
@@ -3817,7 +4656,11 @@
         <v>41353</v>
       </c>
       <c r="C192" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D192" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E192" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3829,7 +4672,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>41395</v>
       </c>
@@ -3837,7 +4680,11 @@
         <v>41395</v>
       </c>
       <c r="C193" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D193" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E193" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3849,7 +4696,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>41444</v>
       </c>
@@ -3857,7 +4704,11 @@
         <v>41444</v>
       </c>
       <c r="C194" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D194" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>UTC-4</v>
       </c>
       <c r="E194" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3869,7 +4720,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>41486</v>
       </c>
@@ -3877,7 +4728,26 @@
         <v>41486</v>
       </c>
       <c r="C195" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D195" s="7" t="str">
+        <f t="shared" ref="D195:D258" si="3">IF(
+ AND(
+  B195 &gt;= IF(
+         YEAR(B195)&gt;=2007,
+         DATE(YEAR(B195),3,14)-WEEKDAY(DATE(YEAR(B195),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B195),4,7)-WEEKDAY(DATE(YEAR(B195),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B195 &lt;  IF(
+         YEAR(B195)&gt;=2007,
+         DATE(YEAR(B195),11,7)-WEEKDAY(DATE(YEAR(B195),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B195),10,31)-WEEKDAY(DATE(YEAR(B195),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
       <c r="E195" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3889,7 +4759,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>41535</v>
       </c>
@@ -3897,7 +4767,11 @@
         <v>41535</v>
       </c>
       <c r="C196" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D196" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E196" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3909,7 +4783,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>41577</v>
       </c>
@@ -3917,7 +4791,11 @@
         <v>41577</v>
       </c>
       <c r="C197" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D197" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E197" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3929,7 +4807,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>41626</v>
       </c>
@@ -3939,6 +4817,10 @@
       <c r="C198" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D198" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E198" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3949,7 +4831,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>41668</v>
       </c>
@@ -3959,6 +4841,10 @@
       <c r="C199" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D199" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E199" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -3969,7 +4855,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>41717</v>
       </c>
@@ -3977,7 +4863,11 @@
         <v>41717</v>
       </c>
       <c r="C200" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D200" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E200" s="3">
         <v>2.5000000000000001E-3</v>
@@ -3989,7 +4879,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>41759</v>
       </c>
@@ -3997,7 +4887,11 @@
         <v>41759</v>
       </c>
       <c r="C201" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D201" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E201" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4009,7 +4903,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>41808</v>
       </c>
@@ -4017,7 +4911,11 @@
         <v>41808</v>
       </c>
       <c r="C202" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D202" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E202" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4029,7 +4927,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>41850</v>
       </c>
@@ -4037,7 +4935,11 @@
         <v>41850</v>
       </c>
       <c r="C203" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D203" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E203" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4049,7 +4951,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>41899</v>
       </c>
@@ -4057,7 +4959,11 @@
         <v>41899</v>
       </c>
       <c r="C204" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D204" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E204" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4069,7 +4975,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>41941</v>
       </c>
@@ -4077,7 +4983,11 @@
         <v>41941</v>
       </c>
       <c r="C205" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D205" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E205" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4089,7 +4999,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>41990</v>
       </c>
@@ -4099,6 +5009,10 @@
       <c r="C206" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D206" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E206" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -4109,7 +5023,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>42032</v>
       </c>
@@ -4119,6 +5033,10 @@
       <c r="C207" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D207" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E207" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -4129,7 +5047,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>42081</v>
       </c>
@@ -4137,7 +5055,11 @@
         <v>42081</v>
       </c>
       <c r="C208" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D208" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E208" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4149,7 +5071,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>42123</v>
       </c>
@@ -4157,7 +5079,11 @@
         <v>42123</v>
       </c>
       <c r="C209" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D209" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E209" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4169,7 +5095,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>42172</v>
       </c>
@@ -4177,7 +5103,11 @@
         <v>42172</v>
       </c>
       <c r="C210" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D210" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E210" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4189,7 +5119,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>42214</v>
       </c>
@@ -4197,7 +5127,11 @@
         <v>42214</v>
       </c>
       <c r="C211" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D211" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E211" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4209,7 +5143,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>42264</v>
       </c>
@@ -4217,7 +5151,11 @@
         <v>42264</v>
       </c>
       <c r="C212" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D212" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E212" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4229,7 +5167,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>42305</v>
       </c>
@@ -4237,7 +5175,11 @@
         <v>42305</v>
       </c>
       <c r="C213" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D213" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E213" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4249,7 +5191,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>42354</v>
       </c>
@@ -4259,6 +5201,10 @@
       <c r="C214" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D214" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E214" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -4269,7 +5215,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>42396</v>
       </c>
@@ -4279,6 +5225,10 @@
       <c r="C215" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D215" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E215" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -4289,7 +5239,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>42445</v>
       </c>
@@ -4297,7 +5247,11 @@
         <v>42445</v>
       </c>
       <c r="C216" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D216" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E216" s="3">
         <v>5.0000000000000001E-3</v>
@@ -4309,7 +5263,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>42487</v>
       </c>
@@ -4317,7 +5271,11 @@
         <v>42487</v>
       </c>
       <c r="C217" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D217" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E217" s="3">
         <v>5.0000000000000001E-3</v>
@@ -4329,7 +5287,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>42536</v>
       </c>
@@ -4337,7 +5295,11 @@
         <v>42536</v>
       </c>
       <c r="C218" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D218" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E218" s="3">
         <v>5.0000000000000001E-3</v>
@@ -4349,7 +5311,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>42578</v>
       </c>
@@ -4357,7 +5319,11 @@
         <v>42578</v>
       </c>
       <c r="C219" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D219" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E219" s="3">
         <v>5.0000000000000001E-3</v>
@@ -4369,7 +5335,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>42634</v>
       </c>
@@ -4377,7 +5343,11 @@
         <v>42634</v>
       </c>
       <c r="C220" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D220" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E220" s="3">
         <v>5.0000000000000001E-3</v>
@@ -4389,7 +5359,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>42676</v>
       </c>
@@ -4397,7 +5367,11 @@
         <v>42676</v>
       </c>
       <c r="C221" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D221" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E221" s="3">
         <v>5.0000000000000001E-3</v>
@@ -4409,7 +5383,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>42718</v>
       </c>
@@ -4419,6 +5393,10 @@
       <c r="C222" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D222" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E222" s="3">
         <v>7.4999999999999997E-3</v>
       </c>
@@ -4429,7 +5407,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>42767</v>
       </c>
@@ -4439,6 +5417,10 @@
       <c r="C223" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D223" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E223" s="3">
         <v>7.4999999999999997E-3</v>
       </c>
@@ -4449,7 +5431,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>42809</v>
       </c>
@@ -4457,7 +5439,11 @@
         <v>42809</v>
       </c>
       <c r="C224" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D224" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E224" s="3">
         <v>0.01</v>
@@ -4469,7 +5455,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>42858</v>
       </c>
@@ -4477,7 +5463,11 @@
         <v>42858</v>
       </c>
       <c r="C225" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D225" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E225" s="3">
         <v>0.01</v>
@@ -4489,7 +5479,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>42900</v>
       </c>
@@ -4497,7 +5487,11 @@
         <v>42900</v>
       </c>
       <c r="C226" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D226" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E226" s="3">
         <v>1.2500000000000001E-2</v>
@@ -4509,7 +5503,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>42942</v>
       </c>
@@ -4517,7 +5511,11 @@
         <v>42942</v>
       </c>
       <c r="C227" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D227" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E227" s="3">
         <v>1.2500000000000001E-2</v>
@@ -4529,7 +5527,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>42998</v>
       </c>
@@ -4537,7 +5535,11 @@
         <v>42998</v>
       </c>
       <c r="C228" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D228" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E228" s="3">
         <v>1.2500000000000001E-2</v>
@@ -4549,7 +5551,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>43040</v>
       </c>
@@ -4557,7 +5559,11 @@
         <v>43040</v>
       </c>
       <c r="C229" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D229" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E229" s="3">
         <v>1.2500000000000001E-2</v>
@@ -4569,7 +5575,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>43082</v>
       </c>
@@ -4579,6 +5585,10 @@
       <c r="C230" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D230" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E230" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -4589,7 +5599,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>43131</v>
       </c>
@@ -4599,6 +5609,10 @@
       <c r="C231" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D231" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E231" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -4609,7 +5623,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>43180</v>
       </c>
@@ -4617,7 +5631,11 @@
         <v>43180</v>
       </c>
       <c r="C232" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D232" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E232" s="3">
         <v>1.7500000000000002E-2</v>
@@ -4629,7 +5647,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>43222</v>
       </c>
@@ -4637,7 +5655,11 @@
         <v>43222</v>
       </c>
       <c r="C233" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D233" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E233" s="3">
         <v>1.7500000000000002E-2</v>
@@ -4649,7 +5671,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>43264</v>
       </c>
@@ -4657,7 +5679,11 @@
         <v>43264</v>
       </c>
       <c r="C234" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D234" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E234" s="3">
         <v>0.02</v>
@@ -4669,7 +5695,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>43313</v>
       </c>
@@ -4677,7 +5703,11 @@
         <v>43313</v>
       </c>
       <c r="C235" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D235" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E235" s="3">
         <v>0.02</v>
@@ -4689,7 +5719,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>43369</v>
       </c>
@@ -4697,7 +5727,11 @@
         <v>43369</v>
       </c>
       <c r="C236" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D236" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E236" s="3">
         <v>2.2499999999999999E-2</v>
@@ -4709,7 +5743,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>43412</v>
       </c>
@@ -4719,6 +5753,10 @@
       <c r="C237" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D237" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E237" s="3">
         <v>2.2499999999999999E-2</v>
       </c>
@@ -4729,7 +5767,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>43453</v>
       </c>
@@ -4739,6 +5777,10 @@
       <c r="C238" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D238" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E238" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -4749,7 +5791,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>43495</v>
       </c>
@@ -4759,6 +5801,10 @@
       <c r="C239" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D239" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E239" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -4769,7 +5815,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>43544</v>
       </c>
@@ -4777,7 +5823,11 @@
         <v>43544</v>
       </c>
       <c r="C240" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D240" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E240" s="3">
         <v>2.5000000000000001E-2</v>
@@ -4789,7 +5839,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>43586</v>
       </c>
@@ -4797,7 +5847,11 @@
         <v>43586</v>
       </c>
       <c r="C241" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D241" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E241" s="3">
         <v>2.5000000000000001E-2</v>
@@ -4809,7 +5863,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>43635</v>
       </c>
@@ -4817,7 +5871,11 @@
         <v>43635</v>
       </c>
       <c r="C242" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D242" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E242" s="3">
         <v>2.5000000000000001E-2</v>
@@ -4829,7 +5887,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>43677</v>
       </c>
@@ -4837,7 +5895,11 @@
         <v>43677</v>
       </c>
       <c r="C243" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D243" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E243" s="3">
         <v>2.2499999999999999E-2</v>
@@ -4849,7 +5911,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>43726</v>
       </c>
@@ -4857,7 +5919,11 @@
         <v>43726</v>
       </c>
       <c r="C244" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D244" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E244" s="3">
         <v>0.02</v>
@@ -4869,7 +5935,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>43768</v>
       </c>
@@ -4877,7 +5943,11 @@
         <v>43768</v>
       </c>
       <c r="C245" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D245" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E245" s="3">
         <v>1.7500000000000002E-2</v>
@@ -4889,7 +5959,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>43810</v>
       </c>
@@ -4899,6 +5969,10 @@
       <c r="C246" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D246" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E246" s="3">
         <v>1.7500000000000002E-2</v>
       </c>
@@ -4909,7 +5983,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>43859</v>
       </c>
@@ -4919,6 +5993,10 @@
       <c r="C247" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D247" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E247" s="3">
         <v>1.7500000000000002E-2</v>
       </c>
@@ -4929,7 +6007,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>43893</v>
       </c>
@@ -4939,6 +6017,10 @@
       <c r="C248" s="2">
         <v>0.41666666666666669</v>
       </c>
+      <c r="D248" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E248" s="3">
         <v>1.2500000000000001E-2</v>
       </c>
@@ -4946,7 +6028,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>43905</v>
       </c>
@@ -4954,7 +6036,11 @@
         <v>43905</v>
       </c>
       <c r="C249" s="2">
-        <v>0.66666666666666663</v>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D249" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E249" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4963,7 +6049,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>43950</v>
       </c>
@@ -4971,7 +6057,11 @@
         <v>43950</v>
       </c>
       <c r="C250" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D250" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E250" s="3">
         <v>2.5000000000000001E-3</v>
@@ -4983,7 +6073,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>43992</v>
       </c>
@@ -4991,7 +6081,11 @@
         <v>43992</v>
       </c>
       <c r="C251" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D251" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E251" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5003,7 +6097,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>44041</v>
       </c>
@@ -5011,7 +6105,11 @@
         <v>44041</v>
       </c>
       <c r="C252" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D252" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E252" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5023,7 +6121,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>44090</v>
       </c>
@@ -5031,7 +6129,11 @@
         <v>44090</v>
       </c>
       <c r="C253" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D253" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E253" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5043,7 +6145,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>44140</v>
       </c>
@@ -5053,6 +6155,10 @@
       <c r="C254" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D254" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E254" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -5063,7 +6169,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>44181</v>
       </c>
@@ -5073,6 +6179,10 @@
       <c r="C255" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D255" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E255" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -5083,7 +6193,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>44223</v>
       </c>
@@ -5093,6 +6203,10 @@
       <c r="C256" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D256" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E256" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -5103,7 +6217,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>44272</v>
       </c>
@@ -5111,7 +6225,11 @@
         <v>44272</v>
       </c>
       <c r="C257" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D257" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E257" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5123,7 +6241,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>44314</v>
       </c>
@@ -5131,7 +6249,11 @@
         <v>44314</v>
       </c>
       <c r="C258" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D258" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
       </c>
       <c r="E258" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5143,7 +6265,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>44363</v>
       </c>
@@ -5151,7 +6273,26 @@
         <v>44363</v>
       </c>
       <c r="C259" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D259" s="7" t="str">
+        <f t="shared" ref="D259:D295" si="4">IF(
+ AND(
+  B259 &gt;= IF(
+         YEAR(B259)&gt;=2007,
+         DATE(YEAR(B259),3,14)-WEEKDAY(DATE(YEAR(B259),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B259),4,7)-WEEKDAY(DATE(YEAR(B259),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B259 &lt;  IF(
+         YEAR(B259)&gt;=2007,
+         DATE(YEAR(B259),11,7)-WEEKDAY(DATE(YEAR(B259),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B259),10,31)-WEEKDAY(DATE(YEAR(B259),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
       <c r="E259" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5163,7 +6304,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>44405</v>
       </c>
@@ -5171,7 +6312,11 @@
         <v>44405</v>
       </c>
       <c r="C260" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D260" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E260" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5183,7 +6328,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>44461</v>
       </c>
@@ -5191,7 +6336,11 @@
         <v>44461</v>
       </c>
       <c r="C261" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D261" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E261" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5203,7 +6352,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>44503</v>
       </c>
@@ -5211,7 +6360,11 @@
         <v>44503</v>
       </c>
       <c r="C262" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D262" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E262" s="3">
         <v>2.5000000000000001E-3</v>
@@ -5223,7 +6376,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>44545</v>
       </c>
@@ -5233,6 +6386,10 @@
       <c r="C263" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D263" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E263" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -5243,7 +6400,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>44587</v>
       </c>
@@ -5253,6 +6410,10 @@
       <c r="C264" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D264" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E264" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
@@ -5263,7 +6424,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>44636</v>
       </c>
@@ -5271,7 +6432,11 @@
         <v>44636</v>
       </c>
       <c r="C265" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D265" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E265" s="3">
         <v>5.0000000000000001E-3</v>
@@ -5283,7 +6448,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>44685</v>
       </c>
@@ -5291,7 +6456,11 @@
         <v>44685</v>
       </c>
       <c r="C266" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D266" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E266" s="3">
         <v>0.01</v>
@@ -5303,7 +6472,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>44727</v>
       </c>
@@ -5311,7 +6480,11 @@
         <v>44727</v>
       </c>
       <c r="C267" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D267" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E267" s="3">
         <v>1.7500000000000002E-2</v>
@@ -5323,7 +6496,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>44769</v>
       </c>
@@ -5331,7 +6504,11 @@
         <v>44769</v>
       </c>
       <c r="C268" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D268" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E268" s="3">
         <v>2.5000000000000001E-2</v>
@@ -5343,7 +6520,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>44825</v>
       </c>
@@ -5351,7 +6528,11 @@
         <v>44825</v>
       </c>
       <c r="C269" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D269" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E269" s="3">
         <v>3.2500000000000001E-2</v>
@@ -5363,7 +6544,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>44867</v>
       </c>
@@ -5371,7 +6552,11 @@
         <v>44867</v>
       </c>
       <c r="C270" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D270" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E270" s="3">
         <v>0.04</v>
@@ -5383,7 +6568,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>44909</v>
       </c>
@@ -5393,6 +6578,10 @@
       <c r="C271" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D271" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E271" s="3">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -5403,7 +6592,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>44958</v>
       </c>
@@ -5413,6 +6602,10 @@
       <c r="C272" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D272" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E272" s="3">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -5423,7 +6616,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>45007</v>
       </c>
@@ -5431,7 +6624,11 @@
         <v>45007</v>
       </c>
       <c r="C273" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D273" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E273" s="3">
         <v>0.05</v>
@@ -5443,7 +6640,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>45049</v>
       </c>
@@ -5451,7 +6648,11 @@
         <v>45049</v>
       </c>
       <c r="C274" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D274" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E274" s="3">
         <v>5.2499999999999998E-2</v>
@@ -5463,7 +6664,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>45091</v>
       </c>
@@ -5471,7 +6672,11 @@
         <v>45091</v>
       </c>
       <c r="C275" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D275" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E275" s="3">
         <v>5.2499999999999998E-2</v>
@@ -5483,7 +6688,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>45133</v>
       </c>
@@ -5491,7 +6696,11 @@
         <v>45133</v>
       </c>
       <c r="C276" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D276" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E276" s="3">
         <v>5.5E-2</v>
@@ -5503,7 +6712,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>45189</v>
       </c>
@@ -5511,7 +6720,11 @@
         <v>45189</v>
       </c>
       <c r="C277" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D277" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E277" s="3">
         <v>5.5E-2</v>
@@ -5523,7 +6736,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>45231</v>
       </c>
@@ -5531,7 +6744,11 @@
         <v>45231</v>
       </c>
       <c r="C278" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D278" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E278" s="3">
         <v>5.5E-2</v>
@@ -5543,7 +6760,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>45273</v>
       </c>
@@ -5553,6 +6770,10 @@
       <c r="C279" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D279" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E279" s="3">
         <v>5.5E-2</v>
       </c>
@@ -5563,7 +6784,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>45322</v>
       </c>
@@ -5573,6 +6794,10 @@
       <c r="C280" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D280" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E280" s="3">
         <v>5.5E-2</v>
       </c>
@@ -5583,7 +6808,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>45371</v>
       </c>
@@ -5591,7 +6816,11 @@
         <v>45371</v>
       </c>
       <c r="C281" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D281" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E281" s="3">
         <v>5.5E-2</v>
@@ -5603,7 +6832,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>45413</v>
       </c>
@@ -5611,7 +6840,11 @@
         <v>45413</v>
       </c>
       <c r="C282" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D282" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E282" s="3">
         <v>5.5E-2</v>
@@ -5623,7 +6856,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>45455</v>
       </c>
@@ -5631,7 +6864,11 @@
         <v>45455</v>
       </c>
       <c r="C283" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D283" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E283" s="3">
         <v>5.5E-2</v>
@@ -5643,7 +6880,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>45504</v>
       </c>
@@ -5651,7 +6888,11 @@
         <v>45504</v>
       </c>
       <c r="C284" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D284" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E284" s="3">
         <v>5.5E-2</v>
@@ -5663,7 +6904,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>45553</v>
       </c>
@@ -5671,7 +6912,11 @@
         <v>45553</v>
       </c>
       <c r="C285" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D285" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E285" s="3">
         <v>0.05</v>
@@ -5683,7 +6928,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>45603</v>
       </c>
@@ -5693,6 +6938,10 @@
       <c r="C286" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D286" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E286" s="3">
         <v>4.7500000000000001E-2</v>
       </c>
@@ -5703,7 +6952,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>45644</v>
       </c>
@@ -5713,6 +6962,10 @@
       <c r="C287" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D287" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E287" s="3">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -5723,7 +6976,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>45686</v>
       </c>
@@ -5733,6 +6986,10 @@
       <c r="C288" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D288" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
+      </c>
       <c r="E288" s="3">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -5743,7 +7000,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>45735</v>
       </c>
@@ -5751,7 +7008,11 @@
         <v>45735</v>
       </c>
       <c r="C289" s="2">
-        <v>0.54166666666666663</v>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D289" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
       </c>
       <c r="E289" s="3">
         <v>4.4999999999999998E-2</v>
@@ -5763,7 +7024,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>45784</v>
       </c>
@@ -5773,6 +7034,10 @@
       <c r="C290" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D290" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
+      </c>
       <c r="E290" s="3">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -5783,7 +7048,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>45826</v>
       </c>
@@ -5793,6 +7058,10 @@
       <c r="C291" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D291" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
+      </c>
       <c r="E291" s="3">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -5803,7 +7072,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>45868</v>
       </c>
@@ -5813,6 +7082,10 @@
       <c r="C292" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D292" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
+      </c>
       <c r="E292" s="3">
         <v>4.4999999999999998E-2</v>
       </c>
@@ -5823,7 +7096,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>45917</v>
       </c>
@@ -5833,6 +7106,10 @@
       <c r="C293" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D293" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
+      </c>
       <c r="E293" s="3">
         <v>4.2500000000000003E-2</v>
       </c>
@@ -5843,7 +7120,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>45959</v>
       </c>
@@ -5853,6 +7130,10 @@
       <c r="C294" s="2">
         <v>0.58333333333333337</v>
       </c>
+      <c r="D294" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-4</v>
+      </c>
       <c r="E294" s="3">
         <v>0.04</v>
       </c>
@@ -5863,7 +7144,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>46001</v>
       </c>
@@ -5872,6 +7153,10 @@
       </c>
       <c r="C295" s="2">
         <v>0.58333333333333337</v>
+      </c>
+      <c r="D295" s="7" t="str">
+        <f t="shared" si="4"/>
+        <v>UTC-5</v>
       </c>
       <c r="E295" s="3">
         <v>3.7499999999999999E-2</v>
@@ -5893,12 +7178,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E03F4A-9B60-4F24-A253-F9B33163B43A}">
   <dimension ref="B2:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="5" t="s">
         <v>5</v>
       </c>

--- a/data/macro/USA/FED Target Rate.xlsx
+++ b/data/macro/USA/FED Target Rate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C97037-02AF-41E7-B536-50828A2F2559}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5F3490-541F-4236-AAF5-45DB20F3A275}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10155" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -139,7 +139,7 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -152,7 +152,7 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -7169,7 +7169,7 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="D296" s="9" t="str">
-        <f t="shared" ref="D296" si="5">IF(
+        <f t="shared" ref="D296:D298" si="5">IF(
  AND(
   B296 &gt;= IF(
          YEAR(B296)&gt;=2007,
@@ -7204,6 +7204,13 @@
       <c r="B297" s="7">
         <v>46099</v>
       </c>
+      <c r="C297" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D297" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="7">
@@ -7212,6 +7219,13 @@
       <c r="B298" s="7">
         <v>46141</v>
       </c>
+      <c r="C298" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D298" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v>UTC-4</v>
+      </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="7">
@@ -7220,6 +7234,28 @@
       <c r="B299" s="7">
         <v>46190</v>
       </c>
+      <c r="C299" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D299" s="9" t="str">
+        <f t="shared" ref="D299:D303" si="6">IF(
+ AND(
+  B299 &gt;= IF(
+         YEAR(B299)&gt;=2007,
+         DATE(YEAR(B299),3,14)-WEEKDAY(DATE(YEAR(B299),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B299),4,7)-WEEKDAY(DATE(YEAR(B299),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B299 &lt;  IF(
+         YEAR(B299)&gt;=2007,
+         DATE(YEAR(B299),11,7)-WEEKDAY(DATE(YEAR(B299),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B299),10,31)-WEEKDAY(DATE(YEAR(B299),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="7">
@@ -7228,6 +7264,13 @@
       <c r="B300" s="7">
         <v>46232</v>
       </c>
+      <c r="C300" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D300" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>UTC-4</v>
+      </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A301" s="7">
@@ -7236,6 +7279,13 @@
       <c r="B301" s="7">
         <v>46281</v>
       </c>
+      <c r="C301" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D301" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>UTC-4</v>
+      </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="7">
@@ -7244,6 +7294,13 @@
       <c r="B302" s="7">
         <v>46323</v>
       </c>
+      <c r="C302" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D302" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>UTC-4</v>
+      </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="7">
@@ -7252,11 +7309,18 @@
       <c r="B303" s="7">
         <v>46365</v>
       </c>
+      <c r="C303" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D303" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>UTC-5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/macro/USA/FED Target Rate.xlsx
+++ b/data/macro/USA/FED Target Rate.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5F3490-541F-4236-AAF5-45DB20F3A275}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A83905-94D4-4644-AFF5-002858089061}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10155" yWindow="780" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fed Target Rate" sheetId="1" r:id="rId1"/>
-    <sheet name="info" sheetId="2" r:id="rId2"/>
+    <sheet name="fig" sheetId="3" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -175,6 +176,2641 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Fed Target Rate'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Fed Target Rate'!$B$2:$B$303</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="302"/>
+                <c:pt idx="0">
+                  <c:v>30221</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30225</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30231</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30274</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30299</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30406</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30461</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30491</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30511</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30517</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30539</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30545</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30574</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30770</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>30868</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>30903</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30945</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>30952</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>30966</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30973</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>31009</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>31022</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>31035</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>31040</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>31071</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>31092</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>31134</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>31162</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31187</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31239</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>31253</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>31280</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>31296</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>31399</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>31478</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>31504</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>31523</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>31554</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>31568</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>31604</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>31645</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>31782</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>31897</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>31919</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>31960</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>32016</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>32023</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>32024</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>32044</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>32085</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>32170</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>32184</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>32232</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>32272</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>32288</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>32316</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>32325</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>32343</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>32363</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>32364</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>32464</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>32469</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>32492</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>32513</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>32548</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>32553</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>32563</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>32645</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>32665</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>32696</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>32716</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>32800</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>32818</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>32862</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>33067</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>33175</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>33191</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>33214</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>33226</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>33247</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>33270</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>33305</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>33358</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>33456</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>33494</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>33542</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>33548</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>33578</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>33592</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>33703</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>33787</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>33851</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>34369</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>34415</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>34442</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>34471</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>34562</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>34653</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>34731</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>34886</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>35052</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>35095</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>35514</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>36067</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>36083</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>36116</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>36341</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>36396</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>36480</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>36558</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>36606</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>36662</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>36894</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>36922</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>36970</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>36999</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>37026</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>37069</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>37124</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>37151</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>37166</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>37201</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>37236</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>37566</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>37797</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>38168</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>38209</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>38251</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>38301</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>38335</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>38385</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>38433</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>38475</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>38533</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>38573</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>38615</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>38657</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>38699</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>38748</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>38804</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>38847</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>38897</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>39343</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>39386</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>39427</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>39469</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>39477</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>39525</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>39568</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>39624</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>39665</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>39707</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>39729</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>39750</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>39798</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>39841</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>39890</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>39932</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>39988</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>40037</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>40079</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>40121</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>40163</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>40205</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>40253</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>40296</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>40352</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>40400</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>40442</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>40485</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>40526</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>40569</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>40617</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>40660</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>40716</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>40764</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>40807</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>40849</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>40890</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>40933</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>40981</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>41024</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>41080</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>41122</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>41165</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>41206</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>41255</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>41304</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>41353</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>41395</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>41444</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>41486</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>41535</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>41577</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>41626</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>41668</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>41717</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>41759</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>41808</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>41850</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>41899</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>41941</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>41990</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>42032</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>42081</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>42123</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>42172</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>42214</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>42264</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>42305</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>42354</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>42396</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>42445</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>42487</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>42536</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>42578</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>42634</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>42676</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>42718</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>42767</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>42809</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>42858</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>42900</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>42942</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>42998</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>43040</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>43082</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>43131</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>43180</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>43222</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>43264</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>43313</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>43369</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>43412</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>43453</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>43495</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>43544</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>43586</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>43635</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>43677</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>43726</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>43768</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>43810</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>43859</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>43893</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>43905</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>43950</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>43992</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>44041</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>44090</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>44140</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>44181</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>44223</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>44272</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>44314</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>44363</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>44405</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>44461</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>44503</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>44545</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>44587</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>44636</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>44685</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>44727</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>44769</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>44825</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>44867</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>44909</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>44958</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>45007</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>45049</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>45091</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>45133</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>45189</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>45231</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>45273</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>45322</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>45371</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>45413</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>45455</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>45504</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>45553</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>45603</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>45644</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>45686</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>45735</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>45784</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>45826</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>45868</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>45917</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>45959</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>46001</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>46190</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>46232</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>46281</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>46323</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>46365</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Fed Target Rate'!$E$2:$E$303</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="302"/>
+                <c:pt idx="0">
+                  <c:v>0.10249999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.6199999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.7499999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.2499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.4299999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.5600000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.3700000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.1125</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.115</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.1125</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.105</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.7499999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8.1199999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8.2500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.3699999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.2500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7.6799999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7.8100000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7.2499999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7.3099999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>6.7500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6.8099999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6.8699999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6.3700000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>5.8700000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>6.7500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>6.6199999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6.7500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>6.8699999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7.2499999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>7.3099999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6.8099999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6.6199999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6.7500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7.2499999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7.4300000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7.6799999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>8.1199999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>8.3099999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>8.3699999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>8.6800000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>9.1200000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>9.3100000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>9.7500000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>9.8100000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>9.5600000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>9.3100000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>9.06E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>8.7499999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>8.2500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>7.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>7.2499999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6.7500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>6.25E-2</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>5.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5.2499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.7500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>3.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>3.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4.2500000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.7500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5.2499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5.2499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4.7500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5.2499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>1.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>1.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>2.2499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>2.75E-2</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>3.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4.2500000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4.7500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5.2499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4.7500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4.2500000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>2.2499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>7.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>7.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>1.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>1.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>1.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>1.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>1.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>1.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>2.2499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>2.2499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>2.2499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>1.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>1.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>1.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>1.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>1.7500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>3.2500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>4.7500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>5.2499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>5.2499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>4.7500000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>4.2500000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D311-4C45-BFD6-D0A714DA2C1A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="678649488"/>
+        <c:axId val="680266112"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="678649488"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+          <c:min val="36526"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="680266112"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="years"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="680266112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="8.0000000000000016E-2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="678649488"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup orientation="portrait"/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B10A5DEF-C617-4F63-8204-E444E72919ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7211,6 +9847,15 @@
         <f t="shared" si="5"/>
         <v>UTC-4</v>
       </c>
+      <c r="E297" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F297" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="G297" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="7">
@@ -7325,6 +9970,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9EAB5-0149-4548-96A8-B9F3C1083AD8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E03F4A-9B60-4F24-A253-F9B33163B43A}">
   <dimension ref="B2:C2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>

--- a/data/macro/USA/FED Target Rate.xlsx
+++ b/data/macro/USA/FED Target Rate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFED5B1-6191-4323-9CF4-59F8A051146B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030A7C9E-F9CA-4200-9969-A98B848E79A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -224,7 +224,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:schemeClr val="accent5"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
               <a:round/>
@@ -234,12 +234,34 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="266"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd" cmpd="sng">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-A480-4BBA-8EEB-D8A3EB9E2FED}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:numRef>
-              <c:f>'Fed Target Rate'!$B$2:$B$303</c:f>
+              <c:f>'Fed Target Rate'!$B$2:$B$1303</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="302"/>
+                <c:ptCount val="1302"/>
                 <c:pt idx="0">
                   <c:v>30221</c:v>
                 </c:pt>
@@ -1145,16 +1167,40 @@
                 </c:pt>
                 <c:pt idx="301">
                   <c:v>46365</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>46414</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>46463</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>46547</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>46596</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>46645</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>46687</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>46729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Fed Target Rate'!$E$2:$E$303</c:f>
+              <c:f>'Fed Target Rate'!$E$2:$E$1303</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="302"/>
+                <c:ptCount val="1302"/>
                 <c:pt idx="0">
                   <c:v>0.10249999999999999</c:v>
                 </c:pt>
@@ -2041,6 +2087,9 @@
                   <c:v>3.7499999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="295">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="296">
                   <c:v>3.7499999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -3085,10 +3134,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G303"/>
+  <dimension ref="A1:G311"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.09765625" style="9" customWidth="1"/>
@@ -9880,6 +9929,15 @@
         <f t="shared" si="5"/>
         <v>UTC-4</v>
       </c>
+      <c r="E298" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F298" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="G298" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="7">
@@ -9892,7 +9950,7 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="D299" s="9" t="str">
-        <f t="shared" ref="D299:D303" si="6">IF(
+        <f t="shared" ref="D299:D304" si="6">IF(
  AND(
   B299 &gt;= IF(
          YEAR(B299)&gt;=2007,
@@ -9910,6 +9968,9 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="G299" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A300" s="7">
@@ -9968,6 +10029,141 @@
       </c>
       <c r="D303" s="9" t="str">
         <f t="shared" si="6"/>
+        <v>UTC-5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A304" s="7">
+        <v>46414</v>
+      </c>
+      <c r="B304" s="7">
+        <v>46414</v>
+      </c>
+      <c r="C304" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D304" s="9" t="str">
+        <f t="shared" si="6"/>
+        <v>UTC-5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A305" s="7">
+        <v>46463</v>
+      </c>
+      <c r="B305" s="7">
+        <v>46463</v>
+      </c>
+      <c r="C305" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D305" s="9" t="str">
+        <f t="shared" ref="D305:D311" si="7">IF(
+ AND(
+  B305 &gt;= IF(
+         YEAR(B305)&gt;=2007,
+         DATE(YEAR(B305),3,14)-WEEKDAY(DATE(YEAR(B305),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B305),4,7)-WEEKDAY(DATE(YEAR(B305),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B305 &lt;  IF(
+         YEAR(B305)&gt;=2007,
+         DATE(YEAR(B305),11,7)-WEEKDAY(DATE(YEAR(B305),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B305),10,31)-WEEKDAY(DATE(YEAR(B305),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A306" s="7">
+        <v>46140</v>
+      </c>
+      <c r="B306" s="7">
+        <v>46140</v>
+      </c>
+      <c r="C306" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D306" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A307" s="7">
+        <v>46547</v>
+      </c>
+      <c r="B307" s="7">
+        <v>46547</v>
+      </c>
+      <c r="C307" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D307" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A308" s="7">
+        <v>46596</v>
+      </c>
+      <c r="B308" s="7">
+        <v>46596</v>
+      </c>
+      <c r="C308" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D308" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A309" s="7">
+        <v>46645</v>
+      </c>
+      <c r="B309" s="7">
+        <v>46645</v>
+      </c>
+      <c r="C309" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D309" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A310" s="7">
+        <v>46687</v>
+      </c>
+      <c r="B310" s="7">
+        <v>46687</v>
+      </c>
+      <c r="C310" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D310" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A311" s="7">
+        <v>46729</v>
+      </c>
+      <c r="B311" s="7">
+        <v>46729</v>
+      </c>
+      <c r="C311" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D311" s="9" t="str">
+        <f t="shared" si="7"/>
         <v>UTC-5</v>
       </c>
     </row>
